--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>filbertgillis</v>
+        <v>myndzi</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>myndzi</v>
+        <v>softlump</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>softlump</v>
+        <v>flippy826</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>flippy826</v>
+        <v>thefishtaco</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>thefishtaco</v>
+        <v>fishtaco(uses weird text)</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>fishtaco(uses weird text)</v>
+        <v>oobusk</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>oobusk</v>
+        <v>rionad</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>rionad</v>
+        <v>rionnad</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>rionnad</v>
+        <v>nolava</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>nolava</v>
+        <v>maito1794</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>maito1794</v>
+        <v>virtualbutt_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>virtualbutt_</v>
+        <v>any_one_plz</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>any_one_plz</v>
+        <v>snekiecr8</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>snekiecr8</v>
+        <v>taianvor</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>taianvor</v>
+        <v>greczko77</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>greczko77</v>
+        <v>kzmz_syndicate</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>kzmz_syndicate</v>
+        <v>hermaeu</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>hermaeu</v>
+        <v>peterce3</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>peterce3</v>
+        <v>superpapipig</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>superpapipig</v>
+        <v>miczupl</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>miczupl</v>
+        <v>kuuucki</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>kuuucki</v>
+        <v>viowlet</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>viowlet</v>
+        <v>vexilus_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>vexilus_</v>
+        <v>shrimp_commander</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>shrimp_commander</v>
+        <v>shankmo</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>shankmo</v>
+        <v>redkelly_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>redkelly_</v>
+        <v>flashfastblack</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>flashfastblack</v>
+        <v>flippy826</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>flippy826</v>
+        <v>nolava</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>nolava</v>
+        <v>juansteed</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>juansteed</v>
+        <v>maito1794</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>maito1794</v>
+        <v>oobusk</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>oobusk</v>
+        <v>taianvor</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>taianvor</v>
+        <v>snekiecr8</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>snekiecr8</v>
+        <v>any_one_plz</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>any_one_plz</v>
+        <v>filbertgillis</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>filbertgillis</v>
+        <v>untoldst0ry</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>untoldst0ry</v>
+        <v>oberonsskills</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>oberonsskills</v>
+        <v>indoorcat_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>indoorcat_</v>
+        <v>evil_moo</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>evil_moo</v>
+        <v>koboldneep</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>koboldneep</v>
+        <v>grimhof</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>grimhof</v>
+        <v>oceantree_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>oceantree_</v>
+        <v>nolava</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>nolava</v>
+        <v>vexilus_</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>vexilus_</v>
+        <v>miczupl</v>
       </c>
     </row>
   </sheetData>
